--- a/artfynd/A 33039-2023 artfynd.xlsx
+++ b/artfynd/A 33039-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118640086</v>
+        <v>118640084</v>
       </c>
       <c r="B3" t="n">
-        <v>97848</v>
+        <v>97880</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534233</v>
+        <v>534200</v>
       </c>
       <c r="R3" t="n">
-        <v>7008150</v>
+        <v>7008125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118640084</v>
+        <v>118640086</v>
       </c>
       <c r="B4" t="n">
-        <v>97880</v>
+        <v>97848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>219811</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534200</v>
+        <v>534233</v>
       </c>
       <c r="R4" t="n">
-        <v>7008125</v>
+        <v>7008150</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33039-2023 artfynd.xlsx
+++ b/artfynd/A 33039-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118640085</v>
+        <v>118640084</v>
       </c>
       <c r="B2" t="n">
-        <v>97869</v>
+        <v>97887</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534233</v>
+        <v>534200</v>
       </c>
       <c r="R2" t="n">
-        <v>7008150</v>
+        <v>7008125</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118640084</v>
+        <v>118640086</v>
       </c>
       <c r="B3" t="n">
-        <v>97880</v>
+        <v>97855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534200</v>
+        <v>534233</v>
       </c>
       <c r="R3" t="n">
-        <v>7008125</v>
+        <v>7008150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118640086</v>
+        <v>118640085</v>
       </c>
       <c r="B4" t="n">
-        <v>97848</v>
+        <v>97876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 33039-2023 artfynd.xlsx
+++ b/artfynd/A 33039-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118640084</v>
+        <v>118640086</v>
       </c>
       <c r="B2" t="n">
-        <v>97887</v>
+        <v>97855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534200</v>
+        <v>534233</v>
       </c>
       <c r="R2" t="n">
-        <v>7008125</v>
+        <v>7008150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118640086</v>
+        <v>118640084</v>
       </c>
       <c r="B3" t="n">
-        <v>97855</v>
+        <v>97887</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534233</v>
+        <v>534200</v>
       </c>
       <c r="R3" t="n">
-        <v>7008150</v>
+        <v>7008125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
